--- a/bench/corpus/clean-11.xlsx
+++ b/bench/corpus/clean-11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nyank\Desktop\後藤さんのclaude\ai-builders-2026\gridlint\bench\corpus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F874F4ED-EF5E-4D14-8E14-53CC754B1852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60D9C873-D3DF-4878-A8D8-5BAEED9AFF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F5405463-0F72-451B-9A33-4D51FBD01F85}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{35056BA2-5A84-4BF4-995C-FABD9F9C5E2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Assumption</t>
   </si>
@@ -72,67 +72,85 @@
     <t>REVENUE</t>
   </si>
   <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Cloud hosting</t>
+  </si>
+  <si>
+    <t>Recruiting</t>
+  </si>
+  <si>
     <t>Contractors</t>
   </si>
   <si>
-    <t>Cloud hosting</t>
+    <t>Total revenue</t>
+  </si>
+  <si>
+    <t>COST OF SALES</t>
+  </si>
+  <si>
+    <t>Insurance</t>
   </si>
   <si>
     <t>Licences</t>
   </si>
   <si>
-    <t>Travel</t>
+    <t>Office rent</t>
   </si>
   <si>
     <t>Software tools</t>
   </si>
   <si>
-    <t>Total revenue</t>
-  </si>
-  <si>
-    <t>COST OF SALES</t>
-  </si>
-  <si>
-    <t>Support</t>
+    <t>Subscriptions</t>
+  </si>
+  <si>
+    <t>Total cost of sales</t>
+  </si>
+  <si>
+    <t>OPERATING COSTS</t>
+  </si>
+  <si>
+    <t>Data vendors</t>
+  </si>
+  <si>
+    <t>Benefits</t>
+  </si>
+  <si>
+    <t>Advertising</t>
+  </si>
+  <si>
+    <t>Services</t>
   </si>
   <si>
     <t>Sponsorships</t>
   </si>
   <si>
-    <t>Services</t>
-  </si>
-  <si>
-    <t>Advertising</t>
-  </si>
-  <si>
-    <t>Total cost of sales</t>
-  </si>
-  <si>
-    <t>OPERATING COSTS</t>
-  </si>
-  <si>
-    <t>Subscriptions</t>
-  </si>
-  <si>
-    <t>Agency fees</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>Events</t>
-  </si>
-  <si>
-    <t>Training</t>
-  </si>
-  <si>
     <t>Total operating costs</t>
   </si>
   <si>
     <t>Grand total</t>
   </si>
   <si>
-    <t>Share of first month</t>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Weighted first month</t>
   </si>
   <si>
     <t>Full year</t>
@@ -534,8 +552,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05C0DB6-0C2A-4370-9DFD-42431DB41283}">
-  <dimension ref="A1:E33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88D9192-D13B-4287-8D3B-F649B5528E14}">
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28.625" customWidth="1"/>
@@ -572,18 +590,18 @@
         <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>7.3999999999999996E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="C6" s="1">
-        <v>169000</v>
+        <v>54000</v>
       </c>
       <c r="D6" s="1">
         <f>C6*(1+$B$6)</f>
-        <v>181506</v>
+        <v>57726</v>
       </c>
       <c r="E6" s="1">
         <f>D6*(1+$B$6)</f>
-        <v>194937.44400000002</v>
+        <v>61709.093999999997</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
@@ -591,18 +609,18 @@
         <v>11</v>
       </c>
       <c r="B7" s="2">
-        <v>3.7999999999999999E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="C7" s="1">
-        <v>47000</v>
+        <v>351000</v>
       </c>
       <c r="D7" s="1">
         <f>C7*(1+$B$7)</f>
-        <v>48786</v>
+        <v>366795</v>
       </c>
       <c r="E7" s="1">
         <f>D7*(1+$B$7)</f>
-        <v>50639.868000000002</v>
+        <v>383300.77499999997</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
@@ -610,18 +628,18 @@
         <v>12</v>
       </c>
       <c r="B8" s="2">
-        <v>8.4000000000000005E-2</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="C8" s="1">
-        <v>260000</v>
+        <v>289000</v>
       </c>
       <c r="D8" s="1">
         <f>C8*(1+$B$8)</f>
-        <v>281840</v>
+        <v>308074</v>
       </c>
       <c r="E8" s="1">
         <f>D8*(1+$B$8)</f>
-        <v>305514.56</v>
+        <v>328406.88400000002</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
@@ -629,78 +647,78 @@
         <v>13</v>
       </c>
       <c r="B9" s="2">
-        <v>-0.02</v>
+        <v>-7.0000000000000001E-3</v>
       </c>
       <c r="C9" s="1">
-        <v>247000</v>
+        <v>98000</v>
       </c>
       <c r="D9" s="1">
         <f>C9*(1+$B$9)</f>
-        <v>242060</v>
+        <v>97314</v>
       </c>
       <c r="E9" s="1">
         <f>D9*(1+$B$9)</f>
-        <v>237218.8</v>
+        <v>96632.801999999996</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="2">
-        <v>8.6999999999999994E-2</v>
-      </c>
       <c r="C10" s="1">
-        <v>151000</v>
+        <f>SUM(C6:C9)</f>
+        <v>792000</v>
       </c>
       <c r="D10" s="1">
-        <f>C10*(1+$B$10)</f>
-        <v>164137</v>
+        <f>SUM(D6:D9)</f>
+        <v>829909</v>
       </c>
       <c r="E10" s="1">
-        <f>D10*(1+$B$10)</f>
-        <v>178416.91899999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
+        <f>SUM(E6:E9)</f>
+        <v>870049.55500000005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
         <v>15</v>
-      </c>
-      <c r="C11" s="1">
-        <f>SUM(C6:C10)</f>
-        <v>874000</v>
-      </c>
-      <c r="D11" s="1">
-        <f>SUM(D6:D10)</f>
-        <v>918329</v>
-      </c>
-      <c r="E11" s="1">
-        <f>SUM(E6:E10)</f>
-        <v>966727.59100000001</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>16</v>
       </c>
+      <c r="B13" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="C13" s="1">
+        <v>384000</v>
+      </c>
+      <c r="D13" s="1">
+        <f>C13*(1+$B$13)</f>
+        <v>384383.99999999994</v>
+      </c>
+      <c r="E13" s="1">
+        <f>D13*(1+$B$13)</f>
+        <v>384768.3839999999</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="2">
-        <v>8.7999999999999995E-2</v>
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="C14" s="1">
-        <v>354000</v>
+        <v>396000</v>
       </c>
       <c r="D14" s="1">
         <f>C14*(1+$B$14)</f>
-        <v>385152</v>
+        <v>431244</v>
       </c>
       <c r="E14" s="1">
         <f>D14*(1+$B$14)</f>
-        <v>419045.37600000005</v>
+        <v>469624.71600000001</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
@@ -708,18 +726,18 @@
         <v>18</v>
       </c>
       <c r="B15" s="2">
-        <v>4.9000000000000002E-2</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="C15" s="1">
-        <v>310000</v>
+        <v>344000</v>
       </c>
       <c r="D15" s="1">
         <f>C15*(1+$B$15)</f>
-        <v>325190</v>
+        <v>369112</v>
       </c>
       <c r="E15" s="1">
         <f>D15*(1+$B$15)</f>
-        <v>341124.31</v>
+        <v>396057.17599999998</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
@@ -727,18 +745,18 @@
         <v>19</v>
       </c>
       <c r="B16" s="2">
-        <v>4.2000000000000003E-2</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="C16" s="1">
-        <v>247000</v>
+        <v>67000</v>
       </c>
       <c r="D16" s="1">
         <f>C16*(1+$B$16)</f>
-        <v>257374</v>
+        <v>65794</v>
       </c>
       <c r="E16" s="1">
         <f>D16*(1+$B$16)</f>
-        <v>268183.70799999998</v>
+        <v>64609.707999999999</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
@@ -746,18 +764,18 @@
         <v>20</v>
       </c>
       <c r="B17" s="2">
-        <v>0.05</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="C17" s="1">
-        <v>221000</v>
+        <v>384000</v>
       </c>
       <c r="D17" s="1">
         <f>C17*(1+$B$17)</f>
-        <v>232050</v>
+        <v>400512</v>
       </c>
       <c r="E17" s="1">
         <f>D17*(1+$B$17)</f>
-        <v>243652.5</v>
+        <v>417734.01599999995</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.4">
@@ -765,16 +783,16 @@
         <v>21</v>
       </c>
       <c r="C18" s="1">
-        <f>SUM(C14:C17)</f>
-        <v>1132000</v>
+        <f>SUM(C13:C17)</f>
+        <v>1575000</v>
       </c>
       <c r="D18" s="1">
-        <f>SUM(D14:D17)</f>
-        <v>1199766</v>
+        <f>SUM(D13:D17)</f>
+        <v>1651046</v>
       </c>
       <c r="E18" s="1">
-        <f>SUM(E14:E17)</f>
-        <v>1272005.8939999999</v>
+        <f>SUM(E13:E17)</f>
+        <v>1732794</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.4">
@@ -787,18 +805,18 @@
         <v>23</v>
       </c>
       <c r="B21" s="2">
-        <v>6.0000000000000001E-3</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="C21" s="1">
-        <v>301000</v>
+        <v>342000</v>
       </c>
       <c r="D21" s="1">
         <f>C21*(1+$B$21)</f>
-        <v>302806</v>
+        <v>358758</v>
       </c>
       <c r="E21" s="1">
         <f>D21*(1+$B$21)</f>
-        <v>304622.83600000001</v>
+        <v>376337.14199999999</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.4">
@@ -806,18 +824,18 @@
         <v>24</v>
       </c>
       <c r="B22" s="2">
-        <v>-2E-3</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="C22" s="1">
-        <v>345000</v>
+        <v>35000</v>
       </c>
       <c r="D22" s="1">
         <f>C22*(1+$B$22)</f>
-        <v>344310</v>
+        <v>37765</v>
       </c>
       <c r="E22" s="1">
         <f>D22*(1+$B$22)</f>
-        <v>343621.38</v>
+        <v>40748.434999999998</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.4">
@@ -825,18 +843,18 @@
         <v>25</v>
       </c>
       <c r="B23" s="2">
-        <v>2.9000000000000001E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="C23" s="1">
-        <v>122000</v>
+        <v>314000</v>
       </c>
       <c r="D23" s="1">
         <f>C23*(1+$B$23)</f>
-        <v>125537.99999999999</v>
+        <v>319652</v>
       </c>
       <c r="E23" s="1">
         <f>D23*(1+$B$23)</f>
-        <v>129178.60199999997</v>
+        <v>325405.73600000003</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.4">
@@ -844,18 +862,18 @@
         <v>26</v>
       </c>
       <c r="B24" s="2">
-        <v>0.02</v>
+        <v>3.1E-2</v>
       </c>
       <c r="C24" s="1">
-        <v>379000</v>
+        <v>395000</v>
       </c>
       <c r="D24" s="1">
         <f>C24*(1+$B$24)</f>
-        <v>386580</v>
+        <v>407244.99999999994</v>
       </c>
       <c r="E24" s="1">
         <f>D24*(1+$B$24)</f>
-        <v>394311.60000000003</v>
+        <v>419869.59499999991</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.4">
@@ -863,18 +881,18 @@
         <v>27</v>
       </c>
       <c r="B25" s="2">
-        <v>6.6000000000000003E-2</v>
+        <v>-1.4999999999999999E-2</v>
       </c>
       <c r="C25" s="1">
-        <v>199000</v>
+        <v>388000</v>
       </c>
       <c r="D25" s="1">
         <f>C25*(1+$B$25)</f>
-        <v>212134</v>
+        <v>382180</v>
       </c>
       <c r="E25" s="1">
         <f>D25*(1+$B$25)</f>
-        <v>226134.84400000001</v>
+        <v>376447.3</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.4">
@@ -883,15 +901,15 @@
       </c>
       <c r="C26" s="1">
         <f>SUM(C21:C25)</f>
-        <v>1346000</v>
+        <v>1474000</v>
       </c>
       <c r="D26" s="1">
         <f>SUM(D21:D25)</f>
-        <v>1371368</v>
+        <v>1505600</v>
       </c>
       <c r="E26" s="1">
         <f>SUM(E21:E25)</f>
-        <v>1397869.2620000001</v>
+        <v>1538808.2080000001</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.4">
@@ -899,60 +917,92 @@
         <v>29</v>
       </c>
       <c r="C28" s="1">
-        <f>SUM(C11,C18,C26)</f>
-        <v>3352000</v>
+        <f>SUM(C10,C18,C26)</f>
+        <v>3841000</v>
       </c>
       <c r="D28" s="1">
-        <f>SUM(D11,D18,D26)</f>
-        <v>3489463</v>
+        <f>SUM(D10,D18,D26)</f>
+        <v>3986555</v>
       </c>
       <c r="E28" s="1">
-        <f>SUM(E11,E18,E26)</f>
-        <v>3636602.747</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
+        <f>SUM(E10,E18,E26)</f>
+        <v>4141651.7630000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="2">
-        <f>C28/$C$28</f>
-        <v>1</v>
-      </c>
-      <c r="D29" s="2">
-        <f>D28/$C$28</f>
-        <v>1.0410092482100239</v>
-      </c>
-      <c r="E29" s="2">
-        <f>E28/$C$28</f>
-        <v>1.0849053541169451</v>
+      <c r="B30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="1">
-        <f>SUM(C28:E28)</f>
-        <v>10478065.747</v>
+        <v>32</v>
+      </c>
+      <c r="B31">
+        <v>0.1</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="1">
-        <f>ROUND(C31/Assumptions!B2,0)</f>
-        <v>105839</v>
+        <v>33</v>
+      </c>
+      <c r="B32">
+        <v>0.3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33">
+        <v>34</v>
+      </c>
+      <c r="B33">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="1">
+        <f>ROUND(C28*VLOOKUP("East",A31:B34,2,FALSE),0)</f>
+        <v>1920500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="1">
+        <f>SUM(C28:E28)</f>
+        <v>11969206.763</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="1">
+        <f>ROUND(C37/Assumptions!B2,0)</f>
+        <v>196217</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39">
         <f>ROUND(Assumptions!B3/AVERAGE(C28:E28),1)</f>
-        <v>1.1000000000000001</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -962,12 +1012,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299A0E2C-E5D1-4ACC-A5D4-8105DF273821}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259A2CBB-8EEC-4D28-9A35-81BBC0FCDBEA}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -982,7 +1029,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -990,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>3700000</v>
+        <v>500000</v>
       </c>
     </row>
   </sheetData>
